--- a/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-SV-thuc-tap-taiDN.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-SV-thuc-tap-taiDN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C334F2-1BD7-497D-9DAB-58A5743901E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F3B7CD-16A2-4ADE-A044-E292E49459F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75213844-687B-4B52-872D-53766ADA4CE5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>DANH SÁCH SINH VIÊN THỰC TẬP TẠI DOANH NGHIỆP</t>
   </si>
@@ -47,37 +47,43 @@
     <t>STT</t>
   </si>
   <si>
-    <t>C23A.TH2</t>
-  </si>
-  <si>
-    <t>Công ty Cổ phần Công nghệ RADA360</t>
-  </si>
-  <si>
     <t>MSSV</t>
   </si>
   <si>
-    <t>Mã doanh nghiệp</t>
+    <t>Công ty TNHH FPT Software</t>
   </si>
   <si>
-    <t>RAD0123</t>
+    <t>HỌ TÊN</t>
   </si>
   <si>
-    <t>Họ</t>
+    <t>LỚP</t>
   </si>
   <si>
-    <t>Tên</t>
+    <t>CÔNG TY THỰC TẬP</t>
   </si>
   <si>
-    <t>Công ty thực tập</t>
+    <t>MÃ VỊ TRÍ</t>
   </si>
   <si>
-    <t>Lớp</t>
+    <t>VỊ TRÍ THỰC TẬP</t>
   </si>
   <si>
-    <t>Phạm Duy</t>
+    <t>Phạm Thị Hồng Anh</t>
   </si>
   <si>
-    <t>Văn</t>
+    <t>C23A.TH1</t>
+  </si>
+  <si>
+    <t>VT_FPT_01</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>MÃ DOANH NGHIỆP</t>
+  </si>
+  <si>
+    <t>DN_FPT</t>
   </si>
 </sst>
 </file>
@@ -160,7 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -183,11 +189,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -221,6 +240,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,77 +581,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F174A1A-AC0E-46EE-8A12-C1F207B9C658}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.09765625" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.796875" customWidth="1"/>
+    <col min="3" max="3" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <f>IF(B3="","",1)</f>
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>2421160052</v>
+        <v>2421160001</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="str">
         <f>IF(B4="","",A3+1)</f>
         <v/>
@@ -638,9 +670,10 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="str">
         <f t="shared" ref="A5:A68" si="0">IF(B5="","",A4+1)</f>
         <v/>
@@ -650,9 +683,10 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -662,9 +696,10 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -674,11 +709,12 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B8="","",A7+1)</f>
         <v/>
       </c>
       <c r="B8" s="3"/>
@@ -686,9 +722,10 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -698,9 +735,10 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -710,9 +748,10 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -722,9 +761,10 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -734,9 +774,10 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -747,8 +788,9 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -758,9 +800,10 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -770,9 +813,10 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -782,9 +826,10 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -794,9 +839,10 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -806,9 +852,10 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -818,9 +865,10 @@
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -830,9 +878,10 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -842,9 +891,10 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -854,9 +904,10 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -866,9 +917,10 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -878,9 +930,10 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -890,9 +943,10 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -902,9 +956,10 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -914,9 +969,10 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -926,9 +982,10 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -938,9 +995,10 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -950,9 +1008,10 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -962,9 +1021,10 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -974,9 +1034,10 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -986,9 +1047,10 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -998,9 +1060,10 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1010,9 +1073,10 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1022,9 +1086,10 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1034,9 +1099,10 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1046,9 +1112,10 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1058,9 +1125,10 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G39" s="4"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1070,9 +1138,10 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G40" s="4"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1082,9 +1151,10 @@
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G41" s="4"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1094,9 +1164,10 @@
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G42" s="4"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1106,9 +1177,10 @@
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G43" s="4"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1118,9 +1190,10 @@
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
-      <c r="G44" s="8"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G44" s="7"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1130,9 +1203,10 @@
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G45" s="4"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1142,9 +1216,10 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G46" s="4"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1154,9 +1229,10 @@
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47" s="4"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1166,9 +1242,10 @@
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G48" s="4"/>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1178,9 +1255,10 @@
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G49" s="4"/>
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1190,9 +1268,10 @@
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G50" s="4"/>
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1202,9 +1281,10 @@
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G51" s="4"/>
+      <c r="H51" s="9"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1214,75 +1294,76 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G52" s="4"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1470,8 +1551,9 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>